--- a/C_集成测试/02_接口文档/例程汇总表.xlsx
+++ b/C_集成测试/02_接口文档/例程汇总表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>例程名称</t>
   </si>
@@ -84,6 +84,24 @@
   </si>
   <si>
     <t>需要修改时序参数</t>
+  </si>
+  <si>
+    <t>顶层 Top</t>
+  </si>
+  <si>
+    <t>自制参考RTL</t>
+  </si>
+  <si>
+    <t>DVP模块与HDMI模块顶层连接，完成接口对接</t>
+  </si>
+  <si>
+    <t>rst_n,cam_pclk,cam_vsync,cam_href,cam_din[7:0],hsync,vsync,rgb_data[15:0]</t>
+  </si>
+  <si>
+    <t>16bit</t>
+  </si>
+  <si>
+    <t>可以，需要修改时钟适配</t>
   </si>
 </sst>
 </file>
@@ -1238,8 +1256,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13.9259259259259" customWidth="1"/>
     <col min="2" max="2" width="18.712962962963" customWidth="1"/>
@@ -1277,22 +1295,22 @@
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1300,23 +1318,46 @@
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
